--- a/Field_Device_Verification.xlsx
+++ b/Field_Device_Verification.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Kontrol Listesi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Sarı hücreler elle doldurulur. Set numarası B1'e girilir; IP şablonlarındaki 'n' bu numaraya göre otomatik çözülür.</t>
+          <t>Yellow cells are filled in by hand. Enter the set number in B1; the 'n' in the IP templates resolves to it automatically.</t>
         </is>
       </c>
       <c r="D1" s="20" t="n"/>
@@ -690,7 +690,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>YATAKLI VAGON — SAHA CİHAZ DOĞRULAMA KONTROL LİSTESİ</t>
+          <t>SLEEPER COACH — FIELD DEVICE VERIFICATION CHECKLIST</t>
         </is>
       </c>
       <c r="B2" s="20" t="n"/>
@@ -719,14 +719,14 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>FİZİKSEL KONTROL</t>
+          <t>PHYSICAL CHECK</t>
         </is>
       </c>
       <c r="B3" s="20" t="n"/>
       <c r="C3" s="21" t="n"/>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>DOĞRULAMA KRİTERİ</t>
+          <t>VERIFICATION CRITERIA</t>
         </is>
       </c>
       <c r="E3" s="20" t="n"/>
@@ -735,7 +735,7 @@
       <c r="H3" s="21" t="n"/>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>YAZILIM KONTROL</t>
+          <t>SOFTWARE CHECK</t>
         </is>
       </c>
       <c r="J3" s="20" t="n"/>
@@ -756,7 +756,7 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Bölüm</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -771,77 +771,77 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Cihaz Tanımı</t>
+          <t>Device definition</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>IP Şablonu</t>
+          <t>IP template</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Beklenen IP</t>
+          <t>Expected IP</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Beklenen Versiyon</t>
+          <t>Expected version</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Beklenen SIP Dahili No</t>
+          <t>Expected SIP extension</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Cihaz İsmi</t>
+          <t>Device name</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Bağlantı Bilgisi</t>
+          <t>Connection info</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>Versiyon</t>
+          <t>Version</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Cihaz Numarası</t>
+          <t>Device number</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>Durum Açıklaması</t>
+          <t>Status description</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>Çalışma Süresi</t>
+          <t>Uptime</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>Hoparlör Ses Seviyesi</t>
+          <t>Speaker volume</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>Mikrofon Ses Seviyesi</t>
+          <t>Microphone volume</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>Hoparlör Gain</t>
+          <t>Speaker gain</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>Mikrofon Gain</t>
+          <t>Microphone gain</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
@@ -851,29 +851,29 @@
       </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
-          <t>SIP Dahili No</t>
+          <t>SIP extension</t>
         </is>
       </c>
       <c r="U4" s="7" t="inlineStr">
         <is>
-          <t>SIP Arama No</t>
+          <t>SIP outbound number</t>
         </is>
       </c>
       <c r="V4" s="7" t="inlineStr">
         <is>
-          <t>Saat Dilimi</t>
+          <t>Time zone</t>
         </is>
       </c>
       <c r="W4" s="7" t="inlineStr">
         <is>
-          <t>Ağ/Zaman Kontrolü</t>
+          <t>Network/time check</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SWITCH   ·   2 kayıt</t>
+          <t xml:space="preserve">  SWITCH   ·   2 records</t>
         </is>
       </c>
       <c r="B5" s="20" t="n"/>
@@ -990,7 +990,7 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PISCU   ·   1 kayıt</t>
+          <t xml:space="preserve">  PISCU   ·   1 records</t>
         </is>
       </c>
       <c r="B8" s="20" t="n"/>
@@ -1065,7 +1065,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ICU   ·   1 kayıt</t>
+          <t xml:space="preserve">  ICU   ·   1 records</t>
         </is>
       </c>
       <c r="B10" s="20" t="n"/>
@@ -1140,7 +1140,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HMI   ·   1 kayıt</t>
+          <t xml:space="preserve">  HMI   ·   1 records</t>
         </is>
       </c>
       <c r="B12" s="20" t="n"/>
@@ -1215,7 +1215,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AP (Access Point)   ·   2 kayıt</t>
+          <t xml:space="preserve">  AP (Access Point)   ·   2 records</t>
         </is>
       </c>
       <c r="B14" s="20" t="n"/>
@@ -1336,7 +1336,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LED · Front   ·   2 kayıt</t>
+          <t xml:space="preserve">  LED · Front   ·   2 records</t>
         </is>
       </c>
       <c r="B17" s="20" t="n"/>
@@ -1457,7 +1457,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LCD · Landing   ·   2 kayıt</t>
+          <t xml:space="preserve">  LCD · Landing   ·   2 records</t>
         </is>
       </c>
       <c r="B20" s="20" t="n"/>
@@ -1578,7 +1578,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LCD · Compartment   ·   11 kayıt   ·   ek alan: Saat Dilimi, SIP PBX IP, SIP Dahili No</t>
+          <t xml:space="preserve">  LCD · Compartment   ·   11 records   ·   extra field: Time zone, SIP PBX IP, SIP extension</t>
         </is>
       </c>
       <c r="B23" s="20" t="n"/>
@@ -2157,7 +2157,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Announcement · UIC   ·   1 kayıt   ·   ek alan: SIP PBX IP, SIP Dahili No</t>
+          <t xml:space="preserve">  Announcement · UIC   ·   1 records   ·   extra field: SIP PBX IP, SIP extension</t>
         </is>
       </c>
       <c r="B35" s="20" t="n"/>
@@ -2236,7 +2236,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Announcement · Amplifier   ·   1 kayıt   ·   ek alan: Hoparlör Ses Seviyesi, Mikrofon Ses Seviyesi, Hoparlör Gain, Mikrofon Gain, SIP PBX IP, SIP Dahili No</t>
+          <t xml:space="preserve">  Announcement · Amplifier   ·   1 records   ·   extra field: Speaker volume, Microphone volume, Speaker gain, Microphone gain, SIP PBX IP, SIP extension</t>
         </is>
       </c>
       <c r="B37" s="20" t="n"/>
@@ -2315,7 +2315,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Announcement · Handset   ·   1 kayıt   ·   ek alan: Hoparlör Ses Seviyesi, Mikrofon Ses Seviyesi, Hoparlör Gain, Mikrofon Gain, SIP PBX IP, SIP Dahili No, SIP Arama No</t>
+          <t xml:space="preserve">  Announcement · Handset   ·   1 records   ·   extra field: Speaker volume, Microphone volume, Speaker gain, Microphone gain, SIP PBX IP, SIP extension, SIP outbound number</t>
         </is>
       </c>
       <c r="B39" s="20" t="n"/>
@@ -2394,7 +2394,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Announcement · Intercom   ·   12 kayıt   ·   ek alan: Hoparlör Ses Seviyesi, Mikrofon Ses Seviyesi, Hoparlör Gain, Mikrofon Gain, SIP PBX IP, SIP Dahili No, SIP Arama No</t>
+          <t xml:space="preserve">  Announcement · Intercom   ·   12 records   ·   extra field: Speaker volume, Microphone volume, Speaker gain, Microphone gain, SIP PBX IP, SIP extension, SIP outbound number</t>
         </is>
       </c>
       <c r="B41" s="20" t="n"/>
@@ -3023,7 +3023,7 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Camera · Corridor   ·   2 kayıt   ·   ek alan: Ağ/Zaman Kontrolü</t>
+          <t xml:space="preserve">  Camera · Corridor   ·   2 records   ·   extra field: Network/time check</t>
         </is>
       </c>
       <c r="B54" s="20" t="n"/>
@@ -3144,7 +3144,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Camera · Landing   ·   2 kayıt   ·   ek alan: Ağ/Zaman Kontrolü</t>
+          <t xml:space="preserve">  Camera · Landing   ·   2 records   ·   extra field: Network/time check</t>
         </is>
       </c>
       <c r="B57" s="20" t="n"/>
@@ -3265,7 +3265,7 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NVR   ·   1 kayıt   ·   ek alan: Ağ/Zaman Kontrolü</t>
+          <t xml:space="preserve">  NVR   ·   1 records   ·   extra field: Network/time check</t>
         </is>
       </c>
       <c r="B60" s="20" t="n"/>
@@ -3337,10 +3337,12 @@
       <c r="V61" s="14" t="n"/>
       <c r="W61" s="15" t="n"/>
     </row>
+    <row r="62"/>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>SONUÇ</t>
+          <t>RESULT</t>
         </is>
       </c>
       <c r="B64" s="20" t="n"/>
@@ -3369,7 +3371,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>Toplam Kayıt</t>
+          <t>Total records</t>
         </is>
       </c>
       <c r="B65" s="19">
@@ -3378,7 +3380,7 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>Versiyon Girilmeyen</t>
+          <t>Version missing</t>
         </is>
       </c>
       <c r="D65" s="19">
@@ -3387,7 +3389,7 @@
       </c>
       <c r="E65" s="18" t="inlineStr">
         <is>
-          <t>Bağlantı Bekleyen</t>
+          <t>Awaiting connection</t>
         </is>
       </c>
       <c r="F65" s="19">
@@ -3396,29 +3398,29 @@
       </c>
       <c r="G65" s="18" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H65" s="19">
-        <f>COUNTIF(M6:M61,"Aktif")</f>
+        <f>COUNTIF(M6:M61,"Active")</f>
         <v/>
       </c>
       <c r="I65" s="18" t="inlineStr">
         <is>
-          <t>Pasif</t>
+          <t>Inactive</t>
         </is>
       </c>
       <c r="J65" s="19">
-        <f>COUNTIF(M6:M61,"Pasif*")</f>
+        <f>COUNTIF(M6:M61,"Inactive*")</f>
         <v/>
       </c>
       <c r="K65" s="18" t="inlineStr">
         <is>
-          <t>Genel Sonuç</t>
+          <t>Overall result</t>
         </is>
       </c>
       <c r="L65" s="19">
-        <f>IF(COUNTIF(M6:M61,"Pasif*")&gt;0,"UYGUN DEĞİL",IF(COUNTA(J6:J61)&lt;COUNTIF(A6:A61,"Yataklı"),"KONTROL BEKLİYOR","UYGUN"))</f>
+        <f>IF(COUNTIF(M6:M61,"Inactive*")&gt;0,"NOT COMPLIANT",IF(COUNTA(J6:J61)&lt;COUNTIF(A6:A61,"Yataklı"),"AWAITING CHECK","COMPLIANT"))</f>
         <v/>
       </c>
       <c r="M65" s="20" t="n"/>
